--- a/output/2026-09-30_19_Malesia_Johor_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-30_19_Malesia_Johor_Componentistica_Ventilazione_industriale.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Produttore/distributore di ventilatori assiali, centrifughi, blower di pressione. Fondata nel 2016.</t>
+          <t>Produttore/distributore di ventilatori assiali, centrifughi, blower di pressione. Fondata nel 2016. [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fornitore/produttore B2B di HVLS fan, dust collector e sistemi di controllo inquinamento aria.</t>
+          <t>Fornitore/produttore B2B di HVLS fan, dust collector e sistemi di controllo inquinamento aria. [DUPLICATO — vedi anche: 2026-09-30_17_Malesia_Johor_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -709,7 +709,6 @@
           <t>07-3521 000</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Rivenditore autorizzato KDK dal 1996, presente nel dealer locator ufficiale KDK; tratta anche ventilatori industriali.</t>
@@ -789,10 +788,9 @@
           <t>018-772 1279</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Produttore/fornitore dal 2014 di condotti flessibili, sistemi di ventilazione e dust collector.</t>
+          <t>Produttore/fornitore dal 2014 di condotti flessibili, sistemi di ventilazione e dust collector. [DUPLICATO — vedi anche: 2026-09-30_18_Malesia_Johor_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -834,7 +832,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fornitore B2B di sistemi LEV, ventilatori a cono, raffreddamento evaporativo.</t>
+          <t>Fornitore B2B di sistemi LEV, ventilatori a cono, raffreddamento evaporativo. [DUPLICATO — vedi anche: 2026-09-30_18_Malesia_Johor_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -911,10 +909,9 @@
           <t>+606-3338889</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fornitore MRO con oltre 300.000 articoli; dust collector confermati nel catalogo online.</t>
+          <t>Fornitore MRO con oltre 300.000 articoli; dust collector confermati nel catalogo online. [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -956,7 +953,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Distributore locale del marchio Purrite: filtri HEPA, housing, cartucce e sacchi filtro anche per dust collector.</t>
+          <t>Distributore locale del marchio Purrite: filtri HEPA, housing, cartucce e sacchi filtro anche per dust collector. [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -991,10 +988,9 @@
           <t>+6014-937 2872</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fornitore B2B di equipaggiamento industriale incl. dust collector/sistemi purificazione aria.</t>
+          <t>Fornitore B2B di equipaggiamento industriale incl. dust collector/sistemi purificazione aria. [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1029,10 +1025,9 @@
           <t>+6012-792 2192</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fornitore soluzioni ambientali incl. dust collector e controllo inquinamento aria.</t>
+          <t>Fornitore soluzioni ambientali incl. dust collector e controllo inquinamento aria. [DUPLICATO — vedi anche: 2026-09-30_17_Malesia_Johor_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1242,7 +1237,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fornitore B2B di sistemi HVAC, ventilazione meccanica e protezione antincendio; oltre 35 anni di attività.</t>
+          <t>Fornitore B2B di sistemi HVAC, ventilazione meccanica e protezione antincendio; oltre 35 anni di attività. [DUPLICATO — vedi anche: 2026-09-30_17_Malesia_Johor_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">

--- a/output/2026-09-30_19_Malesia_Johor_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-30_19_Malesia_Johor_Componentistica_Ventilazione_industriale.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-30_19_Malesia_Johor_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-30_19_Malesia_Johor_Componentistica_Ventilazione_industriale.xlsx
@@ -874,7 +874,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Produttore/installatore dal 2004 di ventilatori di scarico, pad di raffreddamento, sistemi HVLS.</t>
+          <t>Produttore/installatore dal 2004 di ventilatori di scarico, pad di raffreddamento, sistemi HVLS. [DUPLICATO — vedi anche: 2026-09-30_18_Malesia_Johor_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
